--- a/docs/evidence/phase2k/exports/consolidacion-grupo-litoral.xlsx
+++ b/docs/evidence/phase2k/exports/consolidacion-grupo-litoral.xlsx
@@ -319,7 +319,7 @@
     <t>ER_RESULTADO_PNC</t>
   </si>
   <si>
-    <t>elim-reciprocal-1785718073431-mi0ornx</t>
+    <t>elim-reciprocal-1785767198599-go5lho3</t>
   </si>
   <si>
     <t>RECIPROCAL_BALANCE</t>
@@ -340,7 +340,7 @@
     <t>AC_OTROS_CREDITOS</t>
   </si>
   <si>
-    <t>elim-reciprocal-1785718073432-xx56o2n</t>
+    <t>elim-reciprocal-1785767198600-73twjyo</t>
   </si>
   <si>
     <t>Saldos recíprocos — Iberá Distribuciones S.A. / Litoral Holding S.A.</t>
